--- a/samples/ss_lbk_ingest.xlsx
+++ b/samples/ss_lbk_ingest.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:U46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -613,57 +613,72 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Bus 150 kV</t>
+          <t>Bus HV</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Bus LV</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Jumlah Trafo</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Kapasitor</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Catatan Simbol</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit Bay</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Role</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Status Kerawanan</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>Wilayah</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Latitude</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Longitude</t>
         </is>
       </c>
     </row>
@@ -700,24 +715,25 @@
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr">
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -756,24 +772,25 @@
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr">
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -808,42 +825,43 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr">
         <is>
           <t>KMBGN</t>
         </is>
       </c>
-      <c r="I4" t="n">
+      <c r="J4" t="n">
         <v>2</v>
       </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr">
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
         <is>
           <t>2 IBT (unit 1,2)</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr">
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -878,42 +896,43 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr">
         <is>
           <t>NBRJA</t>
         </is>
       </c>
-      <c r="I5" t="n">
+      <c r="J5" t="n">
         <v>2</v>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr">
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
         <is>
           <t>2 IBT (unit 1,2)</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr">
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -952,24 +971,25 @@
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
         <is>
           <t>Rencana</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -1004,42 +1024,43 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
+          <t>1,2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr">
         <is>
           <t>JTAKE</t>
         </is>
       </c>
-      <c r="I7" t="n">
+      <c r="J7" t="n">
         <v>2</v>
       </c>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr">
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
         <is>
           <t>2 IBT (unit 1,2), belum energize -- lihat catatan status IBT-link</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
         <is>
           <t>Rencana</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -1078,28 +1099,29 @@
       <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
       <c r="R8" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -1138,24 +1160,25 @@
       <c r="J9" t="inlineStr"/>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -1194,24 +1217,25 @@
       <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr">
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -1250,28 +1274,29 @@
       <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
+      <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr">
         <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>BOUNDARY</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
         <is>
           <t>KEMBANGAN;BALARAJA</t>
         </is>
@@ -1310,24 +1335,25 @@
       <c r="J12" t="inlineStr"/>
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr">
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q12" t="inlineStr"/>
       <c r="R12" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -1366,24 +1392,25 @@
       <c r="J13" t="inlineStr"/>
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr">
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q13" t="inlineStr"/>
       <c r="R13" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -1422,28 +1449,29 @@
       <c r="J14" t="inlineStr"/>
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr">
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P14" t="inlineStr">
+      <c r="Q14" t="inlineStr">
         <is>
           <t>2;6</t>
         </is>
       </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
       <c r="R14" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -1482,24 +1510,25 @@
       <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr">
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q15" t="inlineStr"/>
       <c r="R15" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -1538,24 +1567,25 @@
       <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr">
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q16" t="inlineStr"/>
       <c r="R16" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -1594,24 +1624,25 @@
       <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr">
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q17" t="inlineStr"/>
       <c r="R17" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -1650,24 +1681,25 @@
       <c r="J18" t="inlineStr"/>
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr">
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q18" t="inlineStr"/>
       <c r="R18" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -1706,24 +1738,25 @@
       <c r="J19" t="inlineStr"/>
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr">
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q19" t="inlineStr"/>
       <c r="R19" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -1762,24 +1795,25 @@
       <c r="J20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr">
+      <c r="M20" t="inlineStr"/>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q20" t="inlineStr"/>
       <c r="R20" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -1816,30 +1850,31 @@
       <c r="H21" t="inlineStr"/>
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr">
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
         <is>
           <t>1 kapasitor</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr">
+      <c r="M21" t="inlineStr"/>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q21" t="inlineStr"/>
       <c r="R21" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -1878,28 +1913,29 @@
       <c r="J22" t="inlineStr"/>
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr">
+      <c r="M22" t="inlineStr"/>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
       <c r="R22" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -1938,24 +1974,25 @@
       <c r="J23" t="inlineStr"/>
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr">
+      <c r="M23" t="inlineStr"/>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q23" t="inlineStr"/>
       <c r="R23" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -1994,24 +2031,25 @@
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr">
+      <c r="M24" t="inlineStr"/>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q24" t="inlineStr"/>
       <c r="R24" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S24" t="inlineStr">
         <is>
           <t>KEMBANGAN;BALARAJA</t>
         </is>
@@ -2048,30 +2086,31 @@
       <c r="H25" t="inlineStr"/>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr">
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
         <is>
           <t>1 kapasitor</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr">
+      <c r="M25" t="inlineStr"/>
+      <c r="N25" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q25" t="inlineStr"/>
       <c r="R25" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S25" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -2110,24 +2149,25 @@
       <c r="J26" t="inlineStr"/>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr">
+      <c r="M26" t="inlineStr"/>
+      <c r="N26" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q26" t="inlineStr"/>
       <c r="R26" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S26" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -2166,24 +2206,25 @@
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr"/>
-      <c r="O27" t="inlineStr">
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q27" t="inlineStr"/>
       <c r="R27" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S27" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -2222,24 +2263,25 @@
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr">
+      <c r="M28" t="inlineStr"/>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q28" t="inlineStr"/>
       <c r="R28" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S28" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -2278,24 +2320,25 @@
       <c r="J29" t="inlineStr"/>
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr">
+      <c r="M29" t="inlineStr"/>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q29" t="inlineStr"/>
       <c r="R29" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S29" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -2334,24 +2377,25 @@
       <c r="J30" t="inlineStr"/>
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr"/>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N30" t="inlineStr"/>
-      <c r="O30" t="inlineStr">
+      <c r="M30" t="inlineStr"/>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q30" t="inlineStr"/>
       <c r="R30" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S30" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -2390,28 +2434,29 @@
       <c r="J31" t="inlineStr"/>
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N31" t="inlineStr"/>
-      <c r="O31" t="inlineStr">
+      <c r="M31" t="inlineStr"/>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
       <c r="R31" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S31" t="inlineStr">
         <is>
           <t>KEMBANGAN;BALARAJA</t>
         </is>
@@ -2450,24 +2495,25 @@
       <c r="J32" t="inlineStr"/>
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr">
+      <c r="M32" t="inlineStr"/>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q32" t="inlineStr"/>
       <c r="R32" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S32" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -2506,28 +2552,29 @@
       <c r="J33" t="inlineStr"/>
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr"/>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N33" t="inlineStr"/>
-      <c r="O33" t="inlineStr">
+      <c r="M33" t="inlineStr"/>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
       <c r="R33" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S33" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -2566,24 +2613,25 @@
       <c r="J34" t="inlineStr"/>
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr"/>
-      <c r="M34" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N34" t="inlineStr"/>
-      <c r="O34" t="inlineStr">
+      <c r="M34" t="inlineStr"/>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q34" t="inlineStr"/>
       <c r="R34" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S34" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -2622,24 +2670,25 @@
       <c r="J35" t="inlineStr"/>
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr">
+      <c r="M35" t="inlineStr"/>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q35" t="inlineStr"/>
       <c r="R35" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S35" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -2678,28 +2727,29 @@
       <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
-      <c r="M36" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N36" t="inlineStr"/>
-      <c r="O36" t="inlineStr">
+      <c r="M36" t="inlineStr"/>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q36" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
       <c r="R36" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S36" t="inlineStr">
         <is>
           <t>KEMBANGAN;BALARAJA</t>
         </is>
@@ -2738,28 +2788,29 @@
       <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr">
+      <c r="M37" t="inlineStr"/>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
       <c r="R37" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S37" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -2798,24 +2849,25 @@
       <c r="J38" t="inlineStr"/>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N38" t="inlineStr"/>
-      <c r="O38" t="inlineStr">
+      <c r="M38" t="inlineStr"/>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q38" t="inlineStr"/>
       <c r="R38" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S38" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -2854,24 +2906,25 @@
       <c r="J39" t="inlineStr"/>
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
-      <c r="M39" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N39" t="inlineStr"/>
-      <c r="O39" t="inlineStr">
+      <c r="M39" t="inlineStr"/>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q39" t="inlineStr"/>
       <c r="R39" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S39" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -2908,34 +2961,35 @@
       <c r="H40" t="inlineStr"/>
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr">
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
         <is>
           <t>1 trafo + 2 kapasitor</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr"/>
-      <c r="M40" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N40" t="inlineStr"/>
-      <c r="O40" t="inlineStr">
+      <c r="M40" t="inlineStr"/>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="Q40" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
       <c r="R40" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S40" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -2972,30 +3026,31 @@
       <c r="H41" t="inlineStr"/>
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr">
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
         <is>
           <t>3 trafo</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr">
+      <c r="M41" t="inlineStr"/>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q41" t="inlineStr"/>
       <c r="R41" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S41" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -3034,24 +3089,25 @@
       <c r="J42" t="inlineStr"/>
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr"/>
-      <c r="M42" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N42" t="inlineStr"/>
-      <c r="O42" t="inlineStr">
+      <c r="M42" t="inlineStr"/>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q42" t="inlineStr"/>
       <c r="R42" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S42" t="inlineStr">
         <is>
           <t>KEMBANGAN;BALARAJA</t>
         </is>
@@ -3090,28 +3146,29 @@
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr">
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" t="inlineStr">
         <is>
           <t>Rawan</t>
         </is>
       </c>
-      <c r="P43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="Q43" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
       <c r="R43" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S43" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -3150,24 +3207,25 @@
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
-      <c r="M44" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N44" t="inlineStr"/>
-      <c r="O44" t="inlineStr">
+      <c r="M44" t="inlineStr"/>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q44" t="inlineStr"/>
       <c r="R44" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S44" t="inlineStr">
         <is>
           <t>BALARAJA</t>
         </is>
@@ -3206,24 +3264,25 @@
       <c r="J45" t="inlineStr"/>
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr">
+      <c r="M45" t="inlineStr"/>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q45" t="inlineStr"/>
       <c r="R45" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S45" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -3262,24 +3321,25 @@
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr">
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
         <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
+      <c r="Q46" t="inlineStr"/>
       <c r="R46" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>

--- a/samples/ss_lbk_ingest.xlsx
+++ b/samples/ss_lbk_ingest.xlsx
@@ -6139,7 +6139,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I10"/>
+  <dimension ref="A1:J10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6165,25 +6165,30 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Jenis</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Tegangan</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Jumlah Sirkit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Status Operasi</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>No Kerawanan</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Sudut Pandang</t>
         </is>
@@ -6208,21 +6213,22 @@
           <t>KMBGN</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G2" t="n">
         <v>1</v>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr">
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -6247,21 +6253,22 @@
           <t>KMBGN</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G3" t="n">
         <v>1</v>
       </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr">
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -6286,21 +6293,22 @@
           <t>SNYAN</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
         <v>1</v>
       </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -6325,21 +6333,22 @@
           <t>SNYAN</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
         <v>1</v>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr">
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -6364,21 +6373,22 @@
           <t>DNYSA</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
         <v>1</v>
       </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr">
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -6403,21 +6413,22 @@
           <t>DNYSA</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
         <v>1</v>
       </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr">
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -6442,21 +6453,22 @@
           <t>CKUPA</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F8" t="n">
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
         <v>1</v>
       </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr">
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -6481,21 +6493,22 @@
           <t>CKUPA</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F9" t="n">
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G9" t="n">
         <v>1</v>
       </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr">
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
@@ -6520,21 +6533,22 @@
           <t>JTAKE</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="F10" t="n">
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
         <v>1</v>
       </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Beroperasi</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr">
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>

--- a/samples/ss_lbk_ingest.xlsx
+++ b/samples/ss_lbk_ingest.xlsx
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U46"/>
+  <dimension ref="A1:U49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,7 +802,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>IBT 1,2 Kembangan</t>
+          <t>IBT 1 Kembangan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -825,7 +825,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H4" t="inlineStr"/>
@@ -835,14 +835,10 @@
         </is>
       </c>
       <c r="J4" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr">
         <is>
@@ -873,12 +869,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>IBT 1,2 New Balaraja</t>
+          <t>IBT 2 Kembangan</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>IBT 1 NBRJA</t>
+          <t>IBT 2 KMBGN</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -896,24 +892,20 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H5" t="inlineStr"/>
       <c r="I5" t="inlineStr">
         <is>
-          <t>NBRJA</t>
+          <t>KMBGN</t>
         </is>
       </c>
       <c r="J5" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2)</t>
-        </is>
-      </c>
+      <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr">
         <is>
@@ -934,7 +926,7 @@
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -944,37 +936,47 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>GITET New Cikupa (rencana)</t>
+          <t>IBT 1 New Balaraja</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>NCKUPA</t>
+          <t>IBT 1 NBRJA</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Busbar GITET</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>500 kV</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NBRJA</t>
+        </is>
+      </c>
+      <c r="J6" t="n">
+        <v>1</v>
+      </c>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr">
         <is>
-          <t>Rencana</t>
+          <t>Beroperasi</t>
         </is>
       </c>
       <c r="O6" t="inlineStr"/>
@@ -1001,12 +1003,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>IBT 1,2 New Cikupa (rencana)</t>
+          <t>IBT 2 New Balaraja</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>IBT 1 NCKUPA</t>
+          <t>IBT 2 NBRJA</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1015,7 +1017,7 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -1024,28 +1026,24 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1,2</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>JTAKE</t>
+          <t>NBRJA</t>
         </is>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>2 IBT (unit 1,2), belum energize -- lihat catatan status IBT-link</t>
-        </is>
-      </c>
+      <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr">
         <is>
-          <t>Rencana</t>
+          <t>Beroperasi</t>
         </is>
       </c>
       <c r="O7" t="inlineStr"/>
@@ -1072,25 +1070,25 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kembangan (bus 150 kV)</t>
+          <t>GITET New Cikupa (rencana)</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>KMBGN</t>
+          <t>NCKUPA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GITET</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>150 kV</t>
+          <t>500 kV</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1102,20 +1100,16 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr">
         <is>
-          <t>Beroperasi</t>
+          <t>Rencana</t>
         </is>
       </c>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1123,7 +1117,7 @@
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>BALARAJA</t>
         </is>
       </c>
     </row>
@@ -1133,37 +1127,47 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New Balaraja (bus 150 kV)</t>
+          <t>IBT 1 New Cikupa (rencana)</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>NBRJA</t>
+          <t>IBT 1 NCKUPA</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>JTAKE</t>
+        </is>
+      </c>
+      <c r="J9" t="n">
+        <v>1</v>
+      </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
       <c r="M9" t="inlineStr"/>
       <c r="N9" t="inlineStr">
         <is>
-          <t>Beroperasi</t>
+          <t>Rencana</t>
         </is>
       </c>
       <c r="O9" t="inlineStr"/>
@@ -1190,37 +1194,47 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Lontar</t>
+          <t>IBT 2 New Cikupa (rencana)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>LTKNG</t>
+          <t>IBT 2 NCKUPA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>IBT 3-Winding</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>150 kV</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
+          <t>500/150 kV</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
       <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>JTAKE</t>
+        </is>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr">
         <is>
-          <t>Beroperasi</t>
+          <t>Rencana</t>
         </is>
       </c>
       <c r="O10" t="inlineStr"/>
@@ -1247,12 +1261,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Durikosambi</t>
+          <t>Kembangan (bus 150 kV)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>DKSBI</t>
+          <t>KMBGN</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1280,17 +1294,17 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>BOUNDARY</t>
-        </is>
-      </c>
+      <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1298,7 +1312,7 @@
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>KEMBANGAN;BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -1308,12 +1322,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Petukangan</t>
+          <t>New Balaraja (bus 150 kV)</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>PKTGN</t>
+          <t>NBRJA</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1355,7 +1369,7 @@
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>BALARAJA</t>
         </is>
       </c>
     </row>
@@ -1365,12 +1379,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Metland</t>
+          <t>Lontar</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>MTLAN</t>
+          <t>LTKNG</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1379,7 +1393,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -1412,7 +1426,7 @@
       </c>
       <c r="S13" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>BALARAJA</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1436,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>New Senayan</t>
+          <t>Durikosambi</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>NSYAN</t>
+          <t>DKSBI</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1436,7 +1450,7 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -1455,17 +1469,17 @@
           <t>Beroperasi</t>
         </is>
       </c>
-      <c r="O14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>BOUNDARY</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>2;6</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr"/>
       <c r="R14" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1473,7 +1487,7 @@
       </c>
       <c r="S14" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>KEMBANGAN;BALARAJA</t>
         </is>
       </c>
     </row>
@@ -1483,12 +1497,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Balaraja</t>
+          <t>Petukangan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>BLRJA</t>
+          <t>PKTGN</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1497,7 +1511,7 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -1530,7 +1544,7 @@
       </c>
       <c r="S15" t="inlineStr">
         <is>
-          <t>BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -1540,12 +1554,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Sindang Jaya</t>
+          <t>Metland</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SDJYA</t>
+          <t>MTLAN</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1587,7 +1601,7 @@
       </c>
       <c r="S16" t="inlineStr">
         <is>
-          <t>BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -1597,12 +1611,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Teluknaga 2 / Dadap</t>
+          <t>New Senayan</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TLKNG2</t>
+          <t>NSYAN</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1633,10 +1647,14 @@
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>2;6</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1644,7 +1662,7 @@
       </c>
       <c r="S17" t="inlineStr">
         <is>
-          <t>BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -1654,12 +1672,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Tangerang Baru</t>
+          <t>Balaraja</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>TGBRU</t>
+          <t>BLRJA</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1711,12 +1729,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Tangerang Baru 3 (belum energize)</t>
+          <t>Sindang Jaya</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>TGBRU3</t>
+          <t>SDJYA</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1768,12 +1786,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Cikande</t>
+          <t>Teluknaga 2 / Dadap</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>CKNDE</t>
+          <t>TLKNG2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1825,12 +1843,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Ciledug</t>
+          <t>Tangerang Baru</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>CLDUG</t>
+          <t>TGBRU</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1839,7 +1857,7 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -1851,11 +1869,7 @@
       <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr"/>
       <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>1 kapasitor</t>
-        </is>
-      </c>
+      <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr">
         <is>
@@ -1876,7 +1890,7 @@
       </c>
       <c r="S21" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>BALARAJA</t>
         </is>
       </c>
     </row>
@@ -1886,21 +1900,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Senayan</t>
+          <t>Tangerang Baru 3 (belum energize)</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>SNYAN</t>
+          <t>TGBRU3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1922,14 +1936,10 @@
       <c r="O22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr"/>
       <c r="R22" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -1937,7 +1947,7 @@
       </c>
       <c r="S22" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>BALARAJA</t>
         </is>
       </c>
     </row>
@@ -1947,12 +1957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Ulujami</t>
+          <t>Cikande</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ULJMI</t>
+          <t>CKNDE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1961,7 +1971,7 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1994,7 +2004,7 @@
       </c>
       <c r="S23" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>BALARAJA</t>
         </is>
       </c>
     </row>
@@ -2004,12 +2014,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Suvarna Sutra</t>
+          <t>Ciledug</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>SVRNA</t>
+          <t>CLDUG</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2030,7 +2040,11 @@
       <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>1 kapasitor</t>
+        </is>
+      </c>
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr">
         <is>
@@ -2051,7 +2065,7 @@
       </c>
       <c r="S24" t="inlineStr">
         <is>
-          <t>KEMBANGAN;BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -2061,17 +2075,17 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Teluknaga</t>
+          <t>Senayan</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>TLKGA</t>
+          <t>SNYAN</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E25" t="n">
@@ -2087,11 +2101,7 @@
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>1 kapasitor</t>
-        </is>
-      </c>
+      <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr">
         <is>
@@ -2101,10 +2111,14 @@
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q25" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2112,7 +2126,7 @@
       </c>
       <c r="S25" t="inlineStr">
         <is>
-          <t>BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -2122,12 +2136,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cikupa Baru</t>
+          <t>Ulujami</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>CKBRU</t>
+          <t>ULJMI</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2169,7 +2183,7 @@
       </c>
       <c r="S26" t="inlineStr">
         <is>
-          <t>BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -2179,12 +2193,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Alam Sutera</t>
+          <t>Suvarna Sutra</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>ALTRA</t>
+          <t>SVRNA</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2193,7 +2207,7 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -2226,7 +2240,7 @@
       </c>
       <c r="S27" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>KEMBANGAN;BALARAJA</t>
         </is>
       </c>
     </row>
@@ -2236,21 +2250,21 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Danayasa</t>
+          <t>Teluknaga</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>DNYSA</t>
+          <t>TLKGA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
@@ -2262,7 +2276,11 @@
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr"/>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>1 kapasitor</t>
+        </is>
+      </c>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr">
         <is>
@@ -2283,7 +2301,7 @@
       </c>
       <c r="S28" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>BALARAJA</t>
         </is>
       </c>
     </row>
@@ -2293,21 +2311,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Abadi Guna Papan</t>
+          <t>Cikupa Baru</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>ABDGP</t>
+          <t>CKBRU</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
@@ -2340,7 +2358,7 @@
       </c>
       <c r="S29" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>BALARAJA</t>
         </is>
       </c>
     </row>
@@ -2350,17 +2368,17 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Mampang</t>
+          <t>Alam Sutera</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MPANG</t>
+          <t>ALTRA</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E30" t="n">
@@ -2407,17 +2425,17 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cikupa</t>
+          <t>Danayasa</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CKUPA</t>
+          <t>DNYSA</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E31" t="n">
@@ -2443,14 +2461,10 @@
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q31" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr"/>
       <c r="R31" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2458,7 +2472,7 @@
       </c>
       <c r="S31" t="inlineStr">
         <is>
-          <t>KEMBANGAN;BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -2468,17 +2482,17 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Sepatan</t>
+          <t>Abadi Guna Papan</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SPTAN</t>
+          <t>ABDGP</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E32" t="n">
@@ -2515,7 +2529,7 @@
       </c>
       <c r="S32" t="inlineStr">
         <is>
-          <t>BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -2525,17 +2539,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cengkareng</t>
+          <t>Mampang</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>CNKNG</t>
+          <t>MPANG</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Busbar GI</t>
+          <t>Busbar GIS</t>
         </is>
       </c>
       <c r="E33" t="n">
@@ -2561,14 +2575,10 @@
       <c r="O33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q33" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr"/>
       <c r="R33" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2576,7 +2586,7 @@
       </c>
       <c r="S33" t="inlineStr">
         <is>
-          <t>BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -2586,12 +2596,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Summarecon Gading Serpong</t>
+          <t>Cikupa</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SGS</t>
+          <t>CKUPA</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -2600,7 +2610,7 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
@@ -2622,10 +2632,14 @@
       <c r="O34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q34" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2633,7 +2647,7 @@
       </c>
       <c r="S34" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>KEMBANGAN;BALARAJA</t>
         </is>
       </c>
     </row>
@@ -2643,12 +2657,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Curug</t>
+          <t>Sepatan</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CURUG</t>
+          <t>SPTAN</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -2657,7 +2671,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
@@ -2690,7 +2704,7 @@
       </c>
       <c r="S35" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>BALARAJA</t>
         </is>
       </c>
     </row>
@@ -2700,12 +2714,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Pasar Kemis</t>
+          <t>Cengkareng</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>PSKMS</t>
+          <t>CNKNG</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2714,7 +2728,7 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
@@ -2741,7 +2755,7 @@
       </c>
       <c r="Q36" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -2751,7 +2765,7 @@
       </c>
       <c r="S36" t="inlineStr">
         <is>
-          <t>KEMBANGAN;BALARAJA</t>
+          <t>BALARAJA</t>
         </is>
       </c>
     </row>
@@ -2761,12 +2775,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Pasar Kemis Baru</t>
+          <t>Summarecon Gading Serpong</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>PSKBR</t>
+          <t>SGS</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2797,14 +2811,10 @@
       <c r="O37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Rawan</t>
-        </is>
-      </c>
-      <c r="Q37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr"/>
       <c r="R37" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2812,7 +2822,7 @@
       </c>
       <c r="S37" t="inlineStr">
         <is>
-          <t>BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -2822,12 +2832,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Sepatan 2</t>
+          <t>Curug</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>SPTAN2</t>
+          <t>CURUG</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2869,7 +2879,7 @@
       </c>
       <c r="S38" t="inlineStr">
         <is>
-          <t>BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -2879,12 +2889,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Tangerang</t>
+          <t>Pasar Kemis</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>TGRNG</t>
+          <t>PSKMS</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2915,10 +2925,14 @@
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Normal</t>
-        </is>
-      </c>
-      <c r="Q39" t="inlineStr"/>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
           <t>Banten</t>
@@ -2926,7 +2940,7 @@
       </c>
       <c r="S39" t="inlineStr">
         <is>
-          <t>BALARAJA</t>
+          <t>KEMBANGAN;BALARAJA</t>
         </is>
       </c>
     </row>
@@ -2936,12 +2950,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Jatake</t>
+          <t>Pasar Kemis Baru</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>JTAKE</t>
+          <t>PSKBR</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2962,11 +2976,7 @@
       <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr"/>
       <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>1 trafo + 2 kapasitor</t>
-        </is>
-      </c>
+      <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr">
         <is>
@@ -2981,7 +2991,7 @@
       </c>
       <c r="Q40" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -2991,7 +3001,7 @@
       </c>
       <c r="S40" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>BALARAJA</t>
         </is>
       </c>
     </row>
@@ -3001,12 +3011,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Maxim</t>
+          <t>Sepatan 2</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>MAXIM</t>
+          <t>SPTAN2</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3015,7 +3025,7 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
@@ -3027,11 +3037,7 @@
       <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr"/>
       <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>3 trafo</t>
-        </is>
-      </c>
+      <c r="L41" t="inlineStr"/>
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr">
         <is>
@@ -3052,7 +3058,7 @@
       </c>
       <c r="S41" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>BALARAJA</t>
         </is>
       </c>
     </row>
@@ -3062,12 +3068,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Jatake Baru</t>
+          <t>Tangerang</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>JTKBR</t>
+          <t>TGRNG</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3076,7 +3082,7 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
@@ -3109,7 +3115,7 @@
       </c>
       <c r="S42" t="inlineStr">
         <is>
-          <t>KEMBANGAN;BALARAJA</t>
+          <t>BALARAJA</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3125,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Gajah Tunggal</t>
+          <t>Jatake</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>GJTGL</t>
+          <t>JTAKE</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3133,7 +3139,7 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
@@ -3145,7 +3151,11 @@
       <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>1 trafo + 2 kapasitor</t>
+        </is>
+      </c>
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr">
         <is>
@@ -3160,7 +3170,7 @@
       </c>
       <c r="Q43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -3170,7 +3180,7 @@
       </c>
       <c r="S43" t="inlineStr">
         <is>
-          <t>BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -3180,21 +3190,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>PLTU Lontar</t>
+          <t>Maxim</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>KIT_LTKNG</t>
+          <t>MAXIM</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
@@ -3206,7 +3216,11 @@
       <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr"/>
       <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>3 trafo</t>
+        </is>
+      </c>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr">
         <is>
@@ -3227,7 +3241,7 @@
       </c>
       <c r="S44" t="inlineStr">
         <is>
-          <t>BALARAJA</t>
+          <t>KEMBANGAN</t>
         </is>
       </c>
     </row>
@@ -3237,21 +3251,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>GIS PLTD Senayan</t>
+          <t>Jatake Baru</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>GISPD</t>
+          <t>JTKBR</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Busbar GIS</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
@@ -3284,7 +3298,7 @@
       </c>
       <c r="S45" t="inlineStr">
         <is>
-          <t>KEMBANGAN</t>
+          <t>KEMBANGAN;BALARAJA</t>
         </is>
       </c>
     </row>
@@ -3294,21 +3308,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>PLTD Senayan</t>
+          <t>Gajah Tunggal</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>KIT_SNYAN</t>
+          <t>GJTGL</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Pembangkit</t>
+          <t>Busbar GI</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
@@ -3330,16 +3344,191 @@
       <c r="O46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
+          <t>Rawan</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R46" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>BALARAJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>PLTU Lontar</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>KIT_LTKNG</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Pembangkit</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr"/>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
           <t>Normal</t>
         </is>
       </c>
-      <c r="Q46" t="inlineStr"/>
-      <c r="R46" t="inlineStr">
-        <is>
-          <t>Banten</t>
-        </is>
-      </c>
-      <c r="S46" t="inlineStr">
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>BALARAJA</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>GIS PLTD Senayan</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>GISPD</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>Busbar GIS</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>2</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr"/>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr"/>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr"/>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>KEMBANGAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>PLTD Senayan</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>KIT_SNYAN</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>Pembangkit</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>2</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>150 kV</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr"/>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr"/>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr"/>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>Beroperasi</t>
+        </is>
+      </c>
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Normal</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
+        <is>
+          <t>Banten</t>
+        </is>
+      </c>
+      <c r="S49" t="inlineStr">
         <is>
           <t>KEMBANGAN</t>
         </is>
